--- a/samples/ss_bll_ingest.xlsx
+++ b/samples/ss_bll_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,57 +536,72 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Longitude</t>
         </is>
       </c>
     </row>
@@ -623,24 +638,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -675,24 +691,25 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -723,42 +740,43 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>NBRJA</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>2 IBT (unit 3,4)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -789,42 +807,43 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>LKBRU</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>2 IBT (unit 1,2)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -859,24 +878,25 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -911,24 +931,25 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -961,30 +982,31 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>KTT LSI 129,6 MVA</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1017,30 +1039,31 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>1 kapasitor non-aktif</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1073,34 +1096,35 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>1 kapasitor aktif</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1133,30 +1157,31 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>KTT SPNML 50 MVA</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1191,24 +1216,25 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1243,24 +1269,25 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1293,30 +1320,31 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>2 kapasitor aktif</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1351,24 +1379,25 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1403,24 +1432,25 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1453,30 +1483,31 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>1 kapasitor + 1 trafo</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1511,24 +1542,25 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_bll_ingest.xlsx
+++ b/samples/ss_bll_ingest.xlsx
@@ -2386,7 +2386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2412,25 +2412,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Tegangan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
@@ -2455,21 +2460,22 @@
           <t>NBRJA</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2490,21 +2496,22 @@
           <t>SRPNG</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2525,21 +2532,22 @@
           <t>SRPNG</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_bll_ingest.xlsx
+++ b/samples/ss_bll_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,7 +717,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IBT 3,4 New Balaraja</t>
+          <t>IBT 3 New Balaraja</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -750,14 +750,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 3,4)</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -784,12 +780,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBT 1,2 Lengkong</t>
+          <t>IBT 4 New Balaraja</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IBT 1 LKBRU</t>
+          <t>IBT 4 NBRJA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -807,24 +803,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LKBRU</t>
+          <t>NBRJA</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -851,31 +843,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New Balaraja (bus 150 kV)</t>
+          <t>IBT 1 Lengkong</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NBRJA</t>
+          <t>IBT 1 LKBRU</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LKBRU</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -904,31 +906,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lengkong Baru (bus 150 kV)</t>
+          <t>IBT 2 Lengkong</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>IBT 2 LKBRU</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>LKBRU</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -957,12 +969,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lautan Steel</t>
+          <t>New Balaraja (bus 150 kV)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LSTEL</t>
+          <t>NBRJA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -971,7 +983,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -983,11 +995,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>KTT LSI 129,6 MVA</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
@@ -1014,12 +1022,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lengkong</t>
+          <t>Lengkong Baru (bus 150 kV)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LKONG</t>
+          <t>LKBRU</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1028,7 +1036,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1040,11 +1048,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1 kapasitor non-aktif</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
@@ -1071,12 +1075,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Serpong</t>
+          <t>Lautan Steel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SRPNG</t>
+          <t>LSTEL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1099,7 +1103,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1 kapasitor aktif</t>
+          <t>KTT LSI 129,6 MVA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1111,14 +1115,10 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spinmill</t>
+          <t>Lengkong</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SPMIL</t>
+          <t>LKONG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>KTT SPNML 50 MVA</t>
+          <t>1 kapasitor non-aktif</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BSD</t>
+          <t>Serpong</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BSD</t>
+          <t>SRPNG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1215,7 +1215,11 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1 kapasitor aktif</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
@@ -1225,10 +1229,14 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1242,12 +1250,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Millenium</t>
+          <t>Spinmill</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MLNUM</t>
+          <t>SPMIL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1256,7 +1264,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1268,7 +1276,11 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>KTT SPNML 50 MVA</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
@@ -1295,12 +1307,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Legok</t>
+          <t>BSD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LEGOK</t>
+          <t>BSD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1309,7 +1321,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1321,11 +1333,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2 kapasitor aktif</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
@@ -1352,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Citra Habitat</t>
+          <t>Millenium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CITRA</t>
+          <t>MLNUM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1366,7 +1374,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1405,12 +1413,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sinar Sahabat</t>
+          <t>Legok</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SSBAT</t>
+          <t>LEGOK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1419,7 +1427,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1431,7 +1439,11 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2 kapasitor aktif</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
@@ -1458,12 +1470,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tigaraksa</t>
+          <t>Citra Habitat</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TGRSA</t>
+          <t>CITRA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1472,7 +1484,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1484,11 +1496,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1 kapasitor + 1 trafo</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
@@ -1515,12 +1523,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tigaraksa 2</t>
+          <t>Sinar Sahabat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TGRSA2</t>
+          <t>SSBAT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1529,7 +1537,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1561,6 +1569,116 @@
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tigaraksa</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TGRSA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1 kapasitor + 1 trafo</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tigaraksa 2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TGRSA2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
